--- a/data/000951_中国重汽_财务数据.xlsx
+++ b/data/000951_中国重汽_财务数据.xlsx
@@ -11003,7 +11003,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>归属于少数股东的综合收益总额</t>
+          <t>minority_common_profit_total</t>
         </is>
       </c>
       <c r="B35" s="3" t="n">
@@ -18096,7 +18096,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC11"/>
+  <dimension ref="A1:AA11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -18126,8 +18126,6 @@
     <col width="16" customWidth="1" min="25" max="25"/>
     <col width="16" customWidth="1" min="26" max="26"/>
     <col width="16" customWidth="1" min="27" max="27"/>
-    <col width="16" customWidth="1" min="28" max="28"/>
-    <col width="16" customWidth="1" min="29" max="29"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -18174,22 +18172,22 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>财务费用率(%)</t>
+          <t>资产负债率(%)</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>资产负债率(%)</t>
+          <t>流动比率</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>流动比率</t>
+          <t>速动比率</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>速动比率</t>
+          <t>产权比率(%)</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
@@ -18199,75 +18197,65 @@
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>应收账款周转天数(天)</t>
+          <t>存货周转率(次)</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>存货周转率(次)</t>
+          <t>总资产周转率(次)</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>存货周转天数(天)</t>
+          <t>流动资产周转率(次)</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>总资产周转率(次)</t>
+          <t>固定资产周转率(次)</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>流动资产周转率(次)</t>
+          <t>营收同比(%)</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>固定资产周转率(次)</t>
+          <t>净利润同比(%)</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>营收同比(%)</t>
+          <t>总资产增长率(%)</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>净利润同比(%)</t>
+          <t>经营现金流/净利润</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>总资产增长率(%)</t>
+          <t>自由现金流(元)</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>经营现金流/净利润</t>
+          <t>现金收入比</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>自由现金流(元)</t>
+          <t>现金流组合</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>现金收入比</t>
+          <t>Altman Z-score</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>现金流组合</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>Altman Z-score</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Z-score判定</t>
         </is>
@@ -18301,58 +18289,52 @@
         <v>2.619114938429419</v>
       </c>
       <c r="I2" s="4" t="inlineStr"/>
-      <c r="J2" s="6" t="n">
-        <v>0.8590486348748865</v>
+      <c r="J2" s="3" t="n">
+        <v>73.19486144607964</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>73.19486144607964</v>
-      </c>
-      <c r="L2" s="3" t="n">
         <v>1.237285830840359</v>
       </c>
-      <c r="M2" s="6" t="n">
+      <c r="L2" s="6" t="n">
         <v>0.9597497960293716</v>
+      </c>
+      <c r="M2" s="3" t="n">
+        <v>273.1129476584022</v>
       </c>
       <c r="N2" s="3" t="n">
         <v>1.656261837377461</v>
       </c>
       <c r="O2" s="3" t="n">
-        <v>217.35693709518</v>
+        <v>5.002047188750613</v>
       </c>
       <c r="P2" s="3" t="n">
-        <v>5.002047188750613</v>
+        <v>1.039474070404095</v>
       </c>
       <c r="Q2" s="3" t="n">
-        <v>71.9705325470788</v>
-      </c>
-      <c r="R2" s="3" t="n">
-        <v>1.039474070404095</v>
-      </c>
-      <c r="S2" s="3" t="n">
         <v>1.160511852313441</v>
       </c>
+      <c r="R2" s="4" t="inlineStr"/>
+      <c r="S2" s="4" t="inlineStr"/>
       <c r="T2" s="4" t="inlineStr"/>
       <c r="U2" s="4" t="inlineStr"/>
-      <c r="V2" s="4" t="inlineStr"/>
-      <c r="W2" s="4" t="inlineStr"/>
-      <c r="X2" s="6" t="n">
+      <c r="V2" s="6" t="n">
         <v>-0.5723094477903677</v>
       </c>
-      <c r="Y2" s="3" t="n">
+      <c r="W2" s="3" t="n">
         <v>-372487600</v>
       </c>
+      <c r="X2" s="3" t="n">
+        <v>1.051944011908983</v>
+      </c>
+      <c r="Y2" s="4" t="inlineStr">
+        <is>
+          <t>−/−/−</t>
+        </is>
+      </c>
       <c r="Z2" s="3" t="n">
-        <v>1.051944011908983</v>
+        <v>1.871564490101979</v>
       </c>
       <c r="AA2" s="4" t="inlineStr">
-        <is>
-          <t>−/−/−</t>
-        </is>
-      </c>
-      <c r="AB2" s="3" t="n">
-        <v>1.871564490101979</v>
-      </c>
-      <c r="AC2" s="4" t="inlineStr">
         <is>
           <t>灰色区</t>
         </is>
@@ -18388,64 +18370,58 @@
       <c r="I3" s="6" t="n">
         <v>0.5260975207935178</v>
       </c>
-      <c r="J3" s="6" t="n">
-        <v>0.6858613748517094</v>
+      <c r="J3" s="3" t="n">
+        <v>76.34480207177209</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>76.34480207177209</v>
-      </c>
-      <c r="L3" s="3" t="n">
         <v>1.215627752226245</v>
       </c>
-      <c r="M3" s="6" t="n">
+      <c r="L3" s="6" t="n">
         <v>0.8182307466484</v>
+      </c>
+      <c r="M3" s="3" t="n">
+        <v>322.7400688145136</v>
       </c>
       <c r="N3" s="3" t="n">
         <v>2.83051281324432</v>
       </c>
       <c r="O3" s="3" t="n">
-        <v>127.1854337897767</v>
+        <v>5.865931786371682</v>
       </c>
       <c r="P3" s="3" t="n">
-        <v>5.865931786371682</v>
+        <v>1.576040916965383</v>
       </c>
       <c r="Q3" s="3" t="n">
-        <v>61.37132396193012</v>
-      </c>
-      <c r="R3" s="3" t="n">
-        <v>1.576040916965383</v>
-      </c>
+        <v>1.733634024012267</v>
+      </c>
+      <c r="R3" s="4" t="inlineStr"/>
       <c r="S3" s="3" t="n">
-        <v>1.733634024012267</v>
-      </c>
-      <c r="T3" s="4" t="inlineStr"/>
+        <v>76.66752228633985</v>
+      </c>
+      <c r="T3" s="3" t="n">
+        <v>117.6892082531263</v>
+      </c>
       <c r="U3" s="3" t="n">
-        <v>76.66752228633985</v>
-      </c>
-      <c r="V3" s="3" t="n">
-        <v>117.6892082531263</v>
+        <v>33.04129546685042</v>
+      </c>
+      <c r="V3" s="6" t="n">
+        <v>0.7571238358391515</v>
       </c>
       <c r="W3" s="3" t="n">
-        <v>33.04129546685042</v>
-      </c>
-      <c r="X3" s="6" t="n">
-        <v>0.7571238358391515</v>
-      </c>
-      <c r="Y3" s="3" t="n">
         <v>710999999.9999999</v>
       </c>
+      <c r="X3" s="3" t="n">
+        <v>1.113147938010133</v>
+      </c>
+      <c r="Y3" s="4" t="inlineStr">
+        <is>
+          <t>+/−/+</t>
+        </is>
+      </c>
       <c r="Z3" s="3" t="n">
-        <v>1.113147938010133</v>
+        <v>2.220513826242151</v>
       </c>
       <c r="AA3" s="4" t="inlineStr">
-        <is>
-          <t>+/−/+</t>
-        </is>
-      </c>
-      <c r="AB3" s="3" t="n">
-        <v>2.220513826242151</v>
-      </c>
-      <c r="AC3" s="4" t="inlineStr">
         <is>
           <t>灰色区</t>
         </is>
@@ -18481,64 +18457,58 @@
       <c r="I4" s="6" t="n">
         <v>0.46930446689389</v>
       </c>
-      <c r="J4" s="6" t="n">
-        <v>0.4573795776449439</v>
+      <c r="J4" s="3" t="n">
+        <v>68.85795892460443</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>68.85795892460443</v>
-      </c>
-      <c r="L4" s="3" t="n">
         <v>1.326666666666667</v>
       </c>
-      <c r="M4" s="6" t="n">
+      <c r="L4" s="6" t="n">
         <v>0.9407333333333333</v>
+      </c>
+      <c r="M4" s="3" t="n">
+        <v>221.1415259172976</v>
       </c>
       <c r="N4" s="3" t="n">
         <v>4.769134755093604</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>75.48539063936227</v>
+        <v>5.556158081233556</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>5.556158081233556</v>
+        <v>1.645155719599894</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>64.792972902613</v>
-      </c>
-      <c r="R4" s="3" t="n">
-        <v>1.645155719599894</v>
-      </c>
+        <v>1.804799615778299</v>
+      </c>
+      <c r="R4" s="4" t="inlineStr"/>
       <c r="S4" s="3" t="n">
-        <v>1.804799615778299</v>
-      </c>
-      <c r="T4" s="4" t="inlineStr"/>
+        <v>8.221499566080205</v>
+      </c>
+      <c r="T4" s="3" t="n">
+        <v>3.559639001583715</v>
+      </c>
       <c r="U4" s="3" t="n">
-        <v>8.221499566080205</v>
+        <v>-18.39807621161672</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>3.559639001583715</v>
+        <v>1.542149788722127</v>
       </c>
       <c r="W4" s="3" t="n">
-        <v>-18.39807621161672</v>
-      </c>
-      <c r="X4" s="3" t="n">
-        <v>1.542149788722127</v>
-      </c>
-      <c r="Y4" s="3" t="n">
         <v>1748000000</v>
       </c>
-      <c r="Z4" s="6" t="n">
+      <c r="X4" s="6" t="n">
         <v>0.9972539567298569</v>
       </c>
+      <c r="Y4" s="4" t="inlineStr">
+        <is>
+          <t>+/−/−</t>
+        </is>
+      </c>
+      <c r="Z4" s="3" t="n">
+        <v>2.94958190624455</v>
+      </c>
       <c r="AA4" s="4" t="inlineStr">
-        <is>
-          <t>+/−/−</t>
-        </is>
-      </c>
-      <c r="AB4" s="3" t="n">
-        <v>2.94958190624455</v>
-      </c>
-      <c r="AC4" s="4" t="inlineStr">
         <is>
           <t>灰色区</t>
         </is>
@@ -18574,64 +18544,58 @@
       <c r="I5" s="6" t="n">
         <v>0.5805748190613633</v>
       </c>
-      <c r="J5" s="6" t="n">
-        <v>0.4143119448767059</v>
+      <c r="J5" s="3" t="n">
+        <v>67.23326250885306</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>67.23326250885306</v>
+        <v>1.368526645768025</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>1.368526645768025</v>
+        <v>1.047523510971787</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>1.047523510971787</v>
+        <v>205.1875397329943</v>
       </c>
       <c r="N5" s="3" t="n">
         <v>11.93971232037758</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>30.15148023169584</v>
+        <v>6.902253387162893</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>6.902253387162893</v>
+        <v>1.730039948462874</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>52.15687976183886</v>
-      </c>
-      <c r="R5" s="3" t="n">
-        <v>1.730039948462874</v>
-      </c>
+        <v>1.909644364124808</v>
+      </c>
+      <c r="R5" s="4" t="inlineStr"/>
       <c r="S5" s="3" t="n">
-        <v>1.909644364124808</v>
-      </c>
-      <c r="T5" s="4" t="inlineStr"/>
+        <v>-1.325129993941674</v>
+      </c>
+      <c r="T5" s="3" t="n">
+        <v>31.16651990198157</v>
+      </c>
       <c r="U5" s="3" t="n">
-        <v>-1.325129993941674</v>
+        <v>8.822596001269439</v>
       </c>
       <c r="V5" s="3" t="n">
-        <v>31.16651990198157</v>
+        <v>1.636329481468138</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>8.822596001269439</v>
-      </c>
-      <c r="X5" s="3" t="n">
-        <v>1.636329481468138</v>
-      </c>
-      <c r="Y5" s="3" t="n">
         <v>2447000000</v>
       </c>
-      <c r="Z5" s="6" t="n">
+      <c r="X5" s="6" t="n">
         <v>0.9909941110347605</v>
       </c>
+      <c r="Y5" s="4" t="inlineStr">
+        <is>
+          <t>+/−/−</t>
+        </is>
+      </c>
+      <c r="Z5" s="3" t="n">
+        <v>2.898820129374381</v>
+      </c>
       <c r="AA5" s="4" t="inlineStr">
-        <is>
-          <t>+/−/−</t>
-        </is>
-      </c>
-      <c r="AB5" s="3" t="n">
-        <v>2.898820129374381</v>
-      </c>
-      <c r="AC5" s="4" t="inlineStr">
         <is>
           <t>灰色区</t>
         </is>
@@ -18667,64 +18631,58 @@
       <c r="I6" s="6" t="n">
         <v>0.7790213090571466</v>
       </c>
-      <c r="J6" s="6" t="n">
-        <v>0.1261453290580783</v>
+      <c r="J6" s="3" t="n">
+        <v>74.54535657515424</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>74.54535657515424</v>
-      </c>
-      <c r="L6" s="3" t="n">
         <v>1.19624867201524</v>
       </c>
-      <c r="M6" s="6" t="n">
+      <c r="L6" s="6" t="n">
         <v>0.8241198666520131</v>
+      </c>
+      <c r="M6" s="3" t="n">
+        <v>292.8866306764052</v>
       </c>
       <c r="N6" s="3" t="n">
         <v>16.67016514499513</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>21.59546692361847</v>
+        <v>7.411890277946067</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>7.411890277946067</v>
+        <v>1.961308206113547</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>48.5706056754743</v>
-      </c>
-      <c r="R6" s="3" t="n">
-        <v>1.961308206113547</v>
-      </c>
+        <v>2.200270870336258</v>
+      </c>
+      <c r="R6" s="4" t="inlineStr"/>
       <c r="S6" s="3" t="n">
-        <v>2.200270870336258</v>
-      </c>
-      <c r="T6" s="4" t="inlineStr"/>
+        <v>50.43508155076124</v>
+      </c>
+      <c r="T6" s="3" t="n">
+        <v>52.19296918716003</v>
+      </c>
       <c r="U6" s="3" t="n">
-        <v>50.43508155076124</v>
+        <v>54.63483731200267</v>
       </c>
       <c r="V6" s="3" t="n">
-        <v>52.19296918716003</v>
+        <v>1.714735410183096</v>
       </c>
       <c r="W6" s="3" t="n">
-        <v>54.63483731200267</v>
-      </c>
-      <c r="X6" s="3" t="n">
-        <v>1.714735410183096</v>
-      </c>
-      <c r="Y6" s="3" t="n">
         <v>3297000000</v>
       </c>
-      <c r="Z6" s="6" t="n">
+      <c r="X6" s="6" t="n">
         <v>0.6238657076552988</v>
       </c>
+      <c r="Y6" s="4" t="inlineStr">
+        <is>
+          <t>+/−/−</t>
+        </is>
+      </c>
+      <c r="Z6" s="3" t="n">
+        <v>2.563643879509207</v>
+      </c>
       <c r="AA6" s="4" t="inlineStr">
-        <is>
-          <t>+/−/−</t>
-        </is>
-      </c>
-      <c r="AB6" s="3" t="n">
-        <v>2.563643879509207</v>
-      </c>
-      <c r="AC6" s="4" t="inlineStr">
         <is>
           <t>灰色区</t>
         </is>
@@ -18760,64 +18718,58 @@
       <c r="I7" s="3" t="n">
         <v>1.073918946322812</v>
       </c>
-      <c r="J7" s="6" t="n">
-        <v>-0.08209539753196157</v>
+      <c r="J7" s="3" t="n">
+        <v>57.78792491121258</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>57.78792491121258</v>
+        <v>1.482655651221819</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>1.482655651221819</v>
+        <v>1.233812770616633</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>1.233812770616633</v>
+        <v>136.9081803005008</v>
       </c>
       <c r="N7" s="3" t="n">
         <v>10.92167312432785</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>32.96198264697245</v>
+        <v>7.126274422689009</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>7.126274422689009</v>
+        <v>1.545538232746333</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>50.51727994838551</v>
-      </c>
-      <c r="R7" s="3" t="n">
-        <v>1.545538232746333</v>
-      </c>
+        <v>1.796754712246297</v>
+      </c>
+      <c r="R7" s="4" t="inlineStr"/>
       <c r="S7" s="3" t="n">
-        <v>1.796754712246297</v>
-      </c>
-      <c r="T7" s="4" t="inlineStr"/>
+        <v>-6.404003721744811</v>
+      </c>
+      <c r="T7" s="3" t="n">
+        <v>-31.09885382453291</v>
+      </c>
       <c r="U7" s="3" t="n">
-        <v>-6.404003721744811</v>
+        <v>-4.415766360427837</v>
       </c>
       <c r="V7" s="3" t="n">
-        <v>-31.09885382453291</v>
+        <v>1.236254731364827</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>-4.415766360427837</v>
-      </c>
-      <c r="X7" s="3" t="n">
-        <v>1.236254731364827</v>
-      </c>
-      <c r="Y7" s="3" t="n">
         <v>1601000000</v>
       </c>
-      <c r="Z7" s="6" t="n">
+      <c r="X7" s="6" t="n">
         <v>0.6698494348226369</v>
       </c>
+      <c r="Y7" s="4" t="inlineStr">
+        <is>
+          <t>+/−/+</t>
+        </is>
+      </c>
+      <c r="Z7" s="3" t="n">
+        <v>2.856478359597666</v>
+      </c>
       <c r="AA7" s="4" t="inlineStr">
-        <is>
-          <t>+/−/+</t>
-        </is>
-      </c>
-      <c r="AB7" s="3" t="n">
-        <v>2.856478359597666</v>
-      </c>
-      <c r="AC7" s="4" t="inlineStr">
         <is>
           <t>灰色区</t>
         </is>
@@ -18853,64 +18805,58 @@
       <c r="I8" s="3" t="n">
         <v>1.503123732133759</v>
       </c>
-      <c r="J8" s="6" t="n">
-        <v>-0.3282421440290733</v>
+      <c r="J8" s="3" t="n">
+        <v>57.54684045153031</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>57.54684045153031</v>
+        <v>1.421762729387439</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>1.421762729387439</v>
+        <v>1.236133367795296</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>1.236133367795296</v>
+        <v>135.5630182989514</v>
       </c>
       <c r="N8" s="3" t="n">
         <v>4.477272584278058</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>80.40609393855982</v>
-      </c>
-      <c r="P8" s="3" t="n">
         <v>6.533055352543359</v>
       </c>
+      <c r="P8" s="6" t="n">
+        <v>0.8252667791350036</v>
+      </c>
       <c r="Q8" s="3" t="n">
-        <v>55.10438540213038</v>
-      </c>
-      <c r="R8" s="6" t="n">
-        <v>0.8252667791350036</v>
-      </c>
+        <v>1.006106720003141</v>
+      </c>
+      <c r="R8" s="4" t="inlineStr"/>
       <c r="S8" s="3" t="n">
-        <v>1.006106720003141</v>
-      </c>
-      <c r="T8" s="4" t="inlineStr"/>
+        <v>-48.62234110667627</v>
+      </c>
+      <c r="T8" s="3" t="n">
+        <v>-68.50175957342508</v>
+      </c>
       <c r="U8" s="3" t="n">
-        <v>-48.62234110667627</v>
+        <v>-3.117424883026101</v>
       </c>
       <c r="V8" s="3" t="n">
-        <v>-68.50175957342508</v>
+        <v>13.37450662247445</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>-3.117424883026101</v>
-      </c>
-      <c r="X8" s="3" t="n">
-        <v>13.37450662247445</v>
-      </c>
-      <c r="Y8" s="3" t="n">
         <v>6574000000</v>
       </c>
-      <c r="Z8" s="6" t="n">
+      <c r="X8" s="6" t="n">
         <v>0.9169243799819885</v>
       </c>
+      <c r="Y8" s="4" t="inlineStr">
+        <is>
+          <t>+/−/−</t>
+        </is>
+      </c>
+      <c r="Z8" s="3" t="n">
+        <v>1.94196457731819</v>
+      </c>
       <c r="AA8" s="4" t="inlineStr">
-        <is>
-          <t>+/−/−</t>
-        </is>
-      </c>
-      <c r="AB8" s="3" t="n">
-        <v>1.94196457731819</v>
-      </c>
-      <c r="AC8" s="4" t="inlineStr">
         <is>
           <t>灰色区</t>
         </is>
@@ -18946,64 +18892,58 @@
       <c r="I9" s="3" t="n">
         <v>1.399766597992972</v>
       </c>
-      <c r="J9" s="6" t="n">
-        <v>-0.5432742788986618</v>
+      <c r="J9" s="3" t="n">
+        <v>57.59782110400992</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>57.59782110400992</v>
+        <v>1.447309470473286</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>1.447309470473286</v>
+        <v>1.252085219960917</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>1.252085219960917</v>
+        <v>135.8369371661155</v>
       </c>
       <c r="N9" s="3" t="n">
         <v>6.861841942523243</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>52.46404726536451</v>
+        <v>10.40979510962404</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>10.40979510962404</v>
+        <v>1.177522999079421</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>34.58281322628277</v>
-      </c>
-      <c r="R9" s="3" t="n">
-        <v>1.177522999079421</v>
-      </c>
+        <v>1.453946879198548</v>
+      </c>
+      <c r="R9" s="4" t="inlineStr"/>
       <c r="S9" s="3" t="n">
-        <v>1.453946879198548</v>
-      </c>
-      <c r="T9" s="4" t="inlineStr"/>
+        <v>45.96248495607909</v>
+      </c>
+      <c r="T9" s="3" t="n">
+        <v>172.2724216563265</v>
+      </c>
       <c r="U9" s="3" t="n">
-        <v>45.96248495607909</v>
+        <v>7.887233794949378</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>172.2724216563265</v>
+        <v>1.476448449454189</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>7.887233794949378</v>
-      </c>
-      <c r="X9" s="3" t="n">
-        <v>1.476448449454189</v>
-      </c>
-      <c r="Y9" s="3" t="n">
         <v>1616000000</v>
       </c>
-      <c r="Z9" s="6" t="n">
+      <c r="X9" s="6" t="n">
         <v>0.8596396588158118</v>
       </c>
+      <c r="Y9" s="4" t="inlineStr">
+        <is>
+          <t>+/−/−</t>
+        </is>
+      </c>
+      <c r="Z9" s="3" t="n">
+        <v>2.370481656981509</v>
+      </c>
       <c r="AA9" s="4" t="inlineStr">
-        <is>
-          <t>+/−/−</t>
-        </is>
-      </c>
-      <c r="AB9" s="3" t="n">
-        <v>2.370481656981509</v>
-      </c>
-      <c r="AC9" s="4" t="inlineStr">
         <is>
           <t>灰色区</t>
         </is>
@@ -19039,64 +18979,58 @@
       <c r="I10" s="3" t="n">
         <v>1.779288238621455</v>
       </c>
-      <c r="J10" s="6" t="n">
-        <v>-0.5602337351494452</v>
+      <c r="J10" s="3" t="n">
+        <v>60.26598960222464</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>60.26598960222464</v>
+        <v>1.244331158238173</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>1.244331158238173</v>
+        <v>1.103466557911909</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>1.103466557911909</v>
+        <v>151.6827947173027</v>
       </c>
       <c r="N10" s="3" t="n">
         <v>5.376865797735759</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>66.95350294061623</v>
+        <v>11.24622126251126</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>11.24622126251126</v>
+        <v>1.145595007671792</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>32.01075202032906</v>
-      </c>
-      <c r="R10" s="3" t="n">
-        <v>1.145595007671792</v>
-      </c>
+        <v>1.476061258139527</v>
+      </c>
+      <c r="R10" s="4" t="inlineStr"/>
       <c r="S10" s="3" t="n">
-        <v>1.476061258139527</v>
-      </c>
-      <c r="T10" s="4" t="inlineStr"/>
+        <v>6.796151304696198</v>
+      </c>
+      <c r="T10" s="3" t="n">
+        <v>30.56617334564508</v>
+      </c>
       <c r="U10" s="3" t="n">
-        <v>6.796151304696198</v>
+        <v>11.5201035514926</v>
       </c>
       <c r="V10" s="3" t="n">
-        <v>30.56617334564508</v>
+        <v>2.824068386905896</v>
       </c>
       <c r="W10" s="3" t="n">
-        <v>11.5201035514926</v>
-      </c>
-      <c r="X10" s="3" t="n">
-        <v>2.824068386905896</v>
-      </c>
-      <c r="Y10" s="3" t="n">
         <v>4914000000</v>
       </c>
-      <c r="Z10" s="6" t="n">
+      <c r="X10" s="6" t="n">
         <v>0.879853107795297</v>
       </c>
+      <c r="Y10" s="4" t="inlineStr">
+        <is>
+          <t>+/−/−</t>
+        </is>
+      </c>
+      <c r="Z10" s="3" t="n">
+        <v>2.156982554016818</v>
+      </c>
       <c r="AA10" s="4" t="inlineStr">
-        <is>
-          <t>+/−/−</t>
-        </is>
-      </c>
-      <c r="AB10" s="3" t="n">
-        <v>2.156982554016818</v>
-      </c>
-      <c r="AC10" s="4" t="inlineStr">
         <is>
           <t>灰色区</t>
         </is>
@@ -19132,64 +19066,58 @@
       <c r="I11" s="3" t="n">
         <v>1.559022469271436</v>
       </c>
-      <c r="J11" s="6" t="n">
-        <v>-0.4635853713712167</v>
+      <c r="J11" s="3" t="n">
+        <v>65.35004683234023</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>65.35004683234023</v>
-      </c>
-      <c r="L11" s="3" t="n">
         <v>1.168681013751002</v>
       </c>
-      <c r="M11" s="6" t="n">
+      <c r="L11" s="6" t="n">
         <v>0.9774002589874824</v>
+      </c>
+      <c r="M11" s="3" t="n">
+        <v>188.5898320680929</v>
       </c>
       <c r="N11" s="3" t="n">
         <v>4.458987695947021</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>80.7358137200559</v>
+        <v>11.35309251203148</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>11.35309251203148</v>
+        <v>1.261546576812332</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>31.70942187060388</v>
-      </c>
-      <c r="R11" s="3" t="n">
-        <v>1.261546576812332</v>
-      </c>
+        <v>1.687827472549404</v>
+      </c>
+      <c r="R11" s="4" t="inlineStr"/>
       <c r="S11" s="3" t="n">
-        <v>1.687827472549404</v>
-      </c>
-      <c r="T11" s="4" t="inlineStr"/>
+        <v>28.50739109643535</v>
+      </c>
+      <c r="T11" s="3" t="n">
+        <v>28.31961127484212</v>
+      </c>
       <c r="U11" s="3" t="n">
-        <v>28.50739109643535</v>
-      </c>
-      <c r="V11" s="3" t="n">
-        <v>28.31961127484212</v>
+        <v>21.33720227300206</v>
+      </c>
+      <c r="V11" s="6" t="n">
+        <v>0.234802909810576</v>
       </c>
       <c r="W11" s="3" t="n">
-        <v>21.33720227300206</v>
+        <v>298000000</v>
       </c>
       <c r="X11" s="6" t="n">
-        <v>0.234802909810576</v>
-      </c>
-      <c r="Y11" s="3" t="n">
-        <v>298000000</v>
-      </c>
-      <c r="Z11" s="6" t="n">
         <v>0.7046410020437277</v>
       </c>
+      <c r="Y11" s="4" t="inlineStr">
+        <is>
+          <t>+/−/−</t>
+        </is>
+      </c>
+      <c r="Z11" s="3" t="n">
+        <v>2.065319427633129</v>
+      </c>
       <c r="AA11" s="4" t="inlineStr">
-        <is>
-          <t>+/−/−</t>
-        </is>
-      </c>
-      <c r="AB11" s="3" t="n">
-        <v>2.065319427633129</v>
-      </c>
-      <c r="AC11" s="4" t="inlineStr">
         <is>
           <t>灰色区</t>
         </is>
